--- a/Sheet.xlsx
+++ b/Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sandip\Documents\Learning\DSA 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C396981-55BA-4E5D-A164-2BF1BFA40B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1150376D-B825-497E-A759-7EE95803F4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2209,7 +2209,7 @@
       <c r="C2" s="28"/>
       <c r="D2" s="27" t="str">
         <f>COUNTIF(I4:I153,"Done")&amp;" Done"</f>
-        <v>7 Done</v>
+        <v>9 Done</v>
       </c>
       <c r="E2" s="28"/>
       <c r="F2" s="28"/>
@@ -2221,7 +2221,7 @@
       <c r="I2" s="28"/>
       <c r="J2" s="27" t="str">
         <f>(150-COUNTIF(I4:I153,"Done"))&amp;" Remaining"</f>
-        <v>143 Remaining</v>
+        <v>141 Remaining</v>
       </c>
       <c r="K2" s="28"/>
       <c r="L2" s="28"/>
@@ -2531,7 +2531,7 @@
         <v>20</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="J11" s="7">
         <v>0</v>
@@ -2565,7 +2565,7 @@
         <v>20</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="J12" s="2">
         <v>0</v>
@@ -6530,15 +6530,15 @@
       </c>
       <c r="C4" s="14">
         <f>COUNTIFS('DSA Tracker'!B$4:B$153,A4,'DSA Tracker'!I$4:I$153,"Done")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="15">
         <f t="shared" ref="D4:D16" si="0">IFERROR(C4/B4,0)</f>
-        <v>0.3888888888888889</v>
+        <v>0.5</v>
       </c>
       <c r="E4" s="16">
         <f t="shared" ref="E4:E16" si="1">B4-C4</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>362</v>
@@ -6788,15 +6788,15 @@
       </c>
       <c r="C16" s="21">
         <f>SUM(C4:C15)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D16" s="22">
         <f t="shared" si="0"/>
-        <v>4.6666666666666669E-2</v>
+        <v>0.06</v>
       </c>
       <c r="E16" s="23">
         <f t="shared" si="1"/>
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
